--- a/extenbooks/XS1202.xlsx
+++ b/extenbooks/XS1202.xlsx
@@ -483,7 +483,7 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.047339473265436</v>
+        <v>-0.06835067234245699</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0429701038351645</v>
+        <v>-0.0586550210225556</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.0319586810436212</v>
+        <v>-0.0391091767496812</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.0426632143678086</v>
+        <v>-0.0489914169605024</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.0543351719987965</v>
+        <v>-0.0490903620499448</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.0498385229419291</v>
+        <v>-0.0392663457437084</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-0.0266917293233082</v>
+        <v>-0.0196289719273057</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0474182115880474</v>
+        <v>-0.0295183483831241</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.0631980563125035</v>
+        <v>-0.0393862249114619</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0515591678424853</v>
+        <v>-0.0196867490061915</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.058667617895136</v>
+        <v>-0.0295681543157476</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.0643401406360585</v>
+        <v>-0.0394420218716467</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.0547344903251545</v>
+        <v>-0.0215439856373429</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0531406090055868</v>
+        <v>-0.0197239865323187</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.0592076999614912</v>
+        <v>-0.0295793646730432</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0456047240498972</v>
+        <v>-0.0197397206251686</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-0.0496858225420206</v>
+        <v>-0.0296591056823256</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.06398971354656791</v>
+        <v>-0.0494791755780569</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.0379916803963121</v>
+        <v>-0.0198377468729295</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-0.0174249430446845</v>
+        <v>0.0099154128978413</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.0306404879856371</v>
+        <v>-0.009930360041185001</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.0371160710879888</v>
+        <v>-0.0100018088233665</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-0.0266665540178998</v>
+        <v>-0.010040271934123</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.0207481815398583</v>
+        <v>0.0400612311687763</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0047009244076627</v>
+        <v>0.0201812949338339</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-0.0078856603692664</v>
+        <v>0.0100925953723757</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.0206142326079444</v>
+        <v>-0.0100946638162466</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-0.0269297760472126</v>
+        <v>-0.0201918318800512</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.011381250820621</v>
+        <v>-0.0100984621947212</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.0234196454721691</v>
+        <v>-0.0100830392881549</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.0034473632356973</v>
+        <v>-0.0100740999787108</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.0044680492663562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.0128403626202235</v>
+        <v>-0.0199824719117349</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.0179165040019704</v>
+        <v>-0.0297515125722356</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.0162481417651726</v>
+        <v>-0.0197587549954505</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-0.0281461061083857</v>
+        <v>-0.0296362958487073</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-0.0319852835171932</v>
+        <v>-0.0295635632043153</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.0321748846429848</v>
+        <v>-0.0392279146299163</v>
       </c>
     </row>
     <row r="41">
@@ -1745,7 +1745,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1964": -0.0167, "1975": 0.09, "1997": 0.006, "2010": 0.161}</t>
+          <t>{"1964": -0.009, "1975": 0.05, "1997": 0.005}</t>
         </is>
       </c>
     </row>
